--- a/test_read_copy.xlsx
+++ b/test_read_copy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="12935"/>
+    <workbookView windowWidth="27948" windowHeight="11855"/>
   </bookViews>
   <sheets>
     <sheet name="0330需求列表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="156">
   <si>
     <t>特性分类</t>
   </si>
@@ -122,277 +122,277 @@
     <t>TSE-C</t>
   </si>
   <si>
+    <t>测试B，测试c</t>
+  </si>
+  <si>
+    <t>进行中</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>待定</t>
+  </si>
+  <si>
+    <t>集成测试</t>
+  </si>
+  <si>
+    <t>fail</t>
+  </si>
+  <si>
+    <t>受阻</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>2024/03/20</t>
+  </si>
+  <si>
+    <t>MySQL+Cassandra</t>
+  </si>
+  <si>
+    <t>关键路径</t>
+  </si>
+  <si>
+    <t>FE9464851392045</t>
+  </si>
+  <si>
+    <t>接口文档自动生成优化</t>
+  </si>
+  <si>
+    <t>张1</t>
+  </si>
+  <si>
+    <t>部分完成</t>
+  </si>
+  <si>
+    <t>2024/03/15</t>
+  </si>
+  <si>
+    <t>开发还未完成</t>
+  </si>
+  <si>
+    <t>pass/fail</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>FE3078712943668</t>
+  </si>
+  <si>
+    <t>报表模块增加自定义筛选条件</t>
+  </si>
+  <si>
+    <t>张2</t>
+  </si>
+  <si>
+    <t>2024/03/25</t>
+  </si>
+  <si>
+    <t>有风险</t>
+  </si>
+  <si>
+    <t>高风险</t>
+  </si>
+  <si>
+    <t>FE3224745170423</t>
+  </si>
+  <si>
+    <t>接口Mock服务搭建</t>
+  </si>
+  <si>
+    <t>2024/04/01</t>
+  </si>
+  <si>
+    <t>资源不足</t>
+  </si>
+  <si>
+    <t>消息中心</t>
+  </si>
+  <si>
+    <t>FE7543708458769</t>
+  </si>
+  <si>
+    <t>周九</t>
+  </si>
+  <si>
+    <t>TSE-D</t>
+  </si>
+  <si>
+    <t>测试F</t>
+  </si>
+  <si>
+    <t>已完成</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>功能测试</t>
+  </si>
+  <si>
+    <t>influxDB</t>
+  </si>
+  <si>
+    <t>报表系统</t>
+  </si>
+  <si>
+    <t>FE3934625576778</t>
+  </si>
+  <si>
+    <t>移动端适配优化，适配小屏设备</t>
+  </si>
+  <si>
+    <t>吴十</t>
+  </si>
+  <si>
+    <t>TSE-B</t>
+  </si>
+  <si>
+    <t>测试A</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>等待上游</t>
+  </si>
+  <si>
+    <t>MySQL</t>
+  </si>
+  <si>
+    <t>优先级调整</t>
+  </si>
+  <si>
+    <t>CES Agent</t>
+  </si>
+  <si>
+    <t>FE2936963796402</t>
+  </si>
+  <si>
+    <t>数据导出功能支持CSV和Excel格式</t>
+  </si>
+  <si>
+    <t>测试D</t>
+  </si>
+  <si>
+    <t>未开始</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>已转</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>订单系统</t>
+  </si>
+  <si>
+    <t>FE7074137600995</t>
+  </si>
+  <si>
+    <t>多环境配置文件管理优化</t>
+  </si>
+  <si>
+    <t>王五</t>
+  </si>
+  <si>
+    <t>TSE-A</t>
+  </si>
+  <si>
+    <t>测试E</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>DI工具</t>
+  </si>
+  <si>
+    <t>FE1999728664845</t>
+  </si>
+  <si>
+    <t>表单验证规则统一</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>回归测试</t>
+  </si>
+  <si>
+    <t>正常推进</t>
+  </si>
+  <si>
+    <t>FE5295143522675</t>
+  </si>
+  <si>
+    <t>页面加载骨架屏支持</t>
+  </si>
+  <si>
+    <t>FE9571751304226</t>
+  </si>
+  <si>
+    <t>代码质量检测规则优化</t>
+  </si>
+  <si>
+    <t>2024/04/10</t>
+  </si>
+  <si>
+    <t>FE4844022164856</t>
+  </si>
+  <si>
+    <t>权限中心</t>
+  </si>
+  <si>
+    <t>FE3344705715228</t>
+  </si>
+  <si>
+    <t>钱七</t>
+  </si>
+  <si>
+    <t>TSET123</t>
+  </si>
+  <si>
+    <t>FE7419749295264</t>
+  </si>
+  <si>
+    <t>缓存机制优化，提高命中率</t>
+  </si>
+  <si>
+    <t>测试C</t>
+  </si>
+  <si>
+    <t>2024/04/05</t>
+  </si>
+  <si>
+    <t>CES项目</t>
+  </si>
+  <si>
+    <t>FE2155481053367</t>
+  </si>
+  <si>
+    <t>API接口增加请求限流保护</t>
+  </si>
+  <si>
+    <t>系统测试</t>
+  </si>
+  <si>
+    <t>需关注</t>
+  </si>
+  <si>
+    <t>FE6673180429603</t>
+  </si>
+  <si>
     <t>测试B</t>
-  </si>
-  <si>
-    <t>进行中</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>待定</t>
-  </si>
-  <si>
-    <t>集成测试</t>
-  </si>
-  <si>
-    <t>fail</t>
-  </si>
-  <si>
-    <t>受阻</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>2024/03/20</t>
-  </si>
-  <si>
-    <t>MySQL+Cassandra</t>
-  </si>
-  <si>
-    <t>关键路径</t>
-  </si>
-  <si>
-    <t>FE9464851392045</t>
-  </si>
-  <si>
-    <t>接口文档自动生成优化</t>
-  </si>
-  <si>
-    <t>张1</t>
-  </si>
-  <si>
-    <t>部分完成</t>
-  </si>
-  <si>
-    <t>2024/03/15</t>
-  </si>
-  <si>
-    <t>开发还未完成</t>
-  </si>
-  <si>
-    <t>pass/fail</t>
-  </si>
-  <si>
-    <t>2024/03/25</t>
-  </si>
-  <si>
-    <t>正常</t>
-  </si>
-  <si>
-    <t>FE3078712943668</t>
-  </si>
-  <si>
-    <t>报表模块增加自定义筛选条件</t>
-  </si>
-  <si>
-    <t>张2</t>
-  </si>
-  <si>
-    <t>测试c</t>
-  </si>
-  <si>
-    <t>有风险</t>
-  </si>
-  <si>
-    <t>高风险</t>
-  </si>
-  <si>
-    <t>FE3224745170423</t>
-  </si>
-  <si>
-    <t>接口Mock服务搭建</t>
-  </si>
-  <si>
-    <t>2024/04/01</t>
-  </si>
-  <si>
-    <t>资源不足</t>
-  </si>
-  <si>
-    <t>消息中心</t>
-  </si>
-  <si>
-    <t>FE7543708458769</t>
-  </si>
-  <si>
-    <t>周九</t>
-  </si>
-  <si>
-    <t>TSE-D</t>
-  </si>
-  <si>
-    <t>测试F</t>
-  </si>
-  <si>
-    <t>已完成</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>功能测试</t>
-  </si>
-  <si>
-    <t>influxDB</t>
-  </si>
-  <si>
-    <t>报表系统</t>
-  </si>
-  <si>
-    <t>FE3934625576778</t>
-  </si>
-  <si>
-    <t>移动端适配优化，适配小屏设备</t>
-  </si>
-  <si>
-    <t>吴十</t>
-  </si>
-  <si>
-    <t>TSE-B</t>
-  </si>
-  <si>
-    <t>测试A</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>等待上游</t>
-  </si>
-  <si>
-    <t>MySQL</t>
-  </si>
-  <si>
-    <t>优先级调整</t>
-  </si>
-  <si>
-    <t>CES Agent</t>
-  </si>
-  <si>
-    <t>FE2936963796402</t>
-  </si>
-  <si>
-    <t>数据导出功能支持CSV和Excel格式</t>
-  </si>
-  <si>
-    <t>测试D</t>
-  </si>
-  <si>
-    <t>未开始</t>
-  </si>
-  <si>
-    <t>0.7</t>
-  </si>
-  <si>
-    <t>已转</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>订单系统</t>
-  </si>
-  <si>
-    <t>FE7074137600995</t>
-  </si>
-  <si>
-    <t>多环境配置文件管理优化</t>
-  </si>
-  <si>
-    <t>王五</t>
-  </si>
-  <si>
-    <t>TSE-A</t>
-  </si>
-  <si>
-    <t>测试E</t>
-  </si>
-  <si>
-    <t>0.3</t>
-  </si>
-  <si>
-    <t>DI工具</t>
-  </si>
-  <si>
-    <t>FE1999728664845</t>
-  </si>
-  <si>
-    <t>表单验证规则统一</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>回归测试</t>
-  </si>
-  <si>
-    <t>正常推进</t>
-  </si>
-  <si>
-    <t>FE5295143522675</t>
-  </si>
-  <si>
-    <t>页面加载骨架屏支持</t>
-  </si>
-  <si>
-    <t>FE9571751304226</t>
-  </si>
-  <si>
-    <t>代码质量检测规则优化</t>
-  </si>
-  <si>
-    <t>2024/04/10</t>
-  </si>
-  <si>
-    <t>FE4844022164856</t>
-  </si>
-  <si>
-    <t>权限中心</t>
-  </si>
-  <si>
-    <t>FE3344705715228</t>
-  </si>
-  <si>
-    <t>钱七</t>
-  </si>
-  <si>
-    <t>TSET123</t>
-  </si>
-  <si>
-    <t>2024/04/05</t>
-  </si>
-  <si>
-    <t>FE7419749295264</t>
-  </si>
-  <si>
-    <t>缓存机制优化，提高命中率</t>
-  </si>
-  <si>
-    <t>测试C</t>
-  </si>
-  <si>
-    <t>CES项目</t>
-  </si>
-  <si>
-    <t>FE2155481053367</t>
-  </si>
-  <si>
-    <t>API接口增加请求限流保护</t>
-  </si>
-  <si>
-    <t>系统测试</t>
-  </si>
-  <si>
-    <t>需关注</t>
-  </si>
-  <si>
-    <t>FE6673180429603</t>
   </si>
   <si>
     <t>pass</t>
@@ -860,12 +860,64 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -990,7 +1042,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -1002,34 +1054,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
@@ -1114,15 +1166,29 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1480,37 +1546,37 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -1519,355 +1585,319 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
       <c r="Y1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
-      <c r="A2" s="3"/>
-      <c r="B2" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>50</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="6">
         <v>0.8</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>6</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y2" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
-      <c r="B3" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:25">
+      <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="1">
         <v>30</v>
       </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="L3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>6</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:25">
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="K3">
-        <v>30</v>
-      </c>
-      <c r="L3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="K4" s="1">
         <v>35</v>
       </c>
-      <c r="N3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="P3" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q3">
+      <c r="L4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="1">
         <v>6</v>
       </c>
-      <c r="R3" t="s">
-        <v>37</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="R4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:25">
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="1">
+        <v>26</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>6</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T3" t="s">
-        <v>39</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y5" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="V3" t="s">
-        <v>38</v>
-      </c>
-      <c r="W3" t="s">
-        <v>39</v>
-      </c>
-      <c r="X3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4">
-        <v>35</v>
-      </c>
-      <c r="L4" t="s">
-        <v>50</v>
-      </c>
-      <c r="M4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="P4" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q4">
-        <v>6</v>
-      </c>
-      <c r="R4" t="s">
-        <v>56</v>
-      </c>
-      <c r="S4" t="s">
-        <v>39</v>
-      </c>
-      <c r="T4" t="s">
-        <v>39</v>
-      </c>
-      <c r="U4" t="s">
-        <v>50</v>
-      </c>
-      <c r="V4" t="s">
-        <v>38</v>
-      </c>
-      <c r="W4" t="s">
-        <v>39</v>
-      </c>
-      <c r="X4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5">
-        <v>26</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="M5" t="s">
-        <v>35</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="P5" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q5">
-        <v>6</v>
-      </c>
-      <c r="R5" t="s">
-        <v>61</v>
-      </c>
-      <c r="S5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T5" t="s">
-        <v>39</v>
-      </c>
-      <c r="U5" t="s">
-        <v>60</v>
-      </c>
-      <c r="V5" t="s">
-        <v>39</v>
-      </c>
-      <c r="W5" t="s">
-        <v>39</v>
-      </c>
-      <c r="X5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:25">
       <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
         <v>62</v>
-      </c>
-      <c r="C6" t="s">
-        <v>63</v>
       </c>
       <c r="D6" t="s">
         <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F6" t="s">
         <v>29</v>
       </c>
       <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" t="s">
         <v>65</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>66</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="K6">
         <v>150</v>
@@ -1876,9 +1906,9 @@
         <v>40</v>
       </c>
       <c r="M6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O6" s="4">
+        <v>68</v>
+      </c>
+      <c r="O6" s="10">
         <v>0.6</v>
       </c>
       <c r="P6" t="s">
@@ -1888,57 +1918,49 @@
         <v>3</v>
       </c>
       <c r="R6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S6" t="s">
         <v>39</v>
       </c>
-      <c r="T6" t="s">
-        <v>39</v>
-      </c>
-      <c r="U6" t="s">
-        <v>68</v>
-      </c>
-      <c r="V6" t="s">
-        <v>38</v>
-      </c>
-      <c r="W6" t="s">
-        <v>39</v>
-      </c>
+      <c r="T6"/>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
       <c r="X6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:25">
       <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
         <v>71</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>72</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>73</v>
-      </c>
-      <c r="E7" t="s">
-        <v>74</v>
       </c>
       <c r="F7" t="s">
         <v>29</v>
       </c>
       <c r="G7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" t="s">
         <v>75</v>
-      </c>
-      <c r="H7" t="s">
-        <v>76</v>
       </c>
       <c r="I7" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="4" t="s">
-        <v>77</v>
+      <c r="J7" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="K7">
         <v>30</v>
@@ -1947,9 +1969,9 @@
         <v>47</v>
       </c>
       <c r="M7" t="s">
-        <v>69</v>
-      </c>
-      <c r="O7" s="4">
+        <v>68</v>
+      </c>
+      <c r="O7" s="10">
         <v>1</v>
       </c>
       <c r="P7" t="s">
@@ -1959,42 +1981,34 @@
         <v>5</v>
       </c>
       <c r="R7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S7" t="s">
         <v>38</v>
       </c>
-      <c r="T7" t="s">
-        <v>38</v>
-      </c>
-      <c r="U7" t="s">
-        <v>50</v>
-      </c>
-      <c r="V7" t="s">
-        <v>38</v>
-      </c>
-      <c r="W7" t="s">
-        <v>39</v>
-      </c>
+      <c r="T7"/>
+      <c r="U7"/>
+      <c r="V7"/>
+      <c r="W7"/>
       <c r="X7" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y7" t="s">
         <v>79</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:25">
       <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
         <v>81</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>82</v>
       </c>
-      <c r="D8" t="s">
-        <v>83</v>
-      </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F8" t="s">
         <v>29</v>
@@ -2003,24 +2017,24 @@
         <v>30</v>
       </c>
       <c r="H8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8" t="s">
         <v>84</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="K8">
         <v>150</v>
       </c>
       <c r="L8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M8" t="s">
         <v>35</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O8" s="10">
         <v>0.4</v>
       </c>
       <c r="P8" t="s">
@@ -2030,57 +2044,49 @@
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>68</v>
-      </c>
-      <c r="T8" t="s">
-        <v>68</v>
-      </c>
-      <c r="U8" t="s">
-        <v>40</v>
-      </c>
-      <c r="V8" t="s">
-        <v>68</v>
-      </c>
-      <c r="W8" t="s">
-        <v>38</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
       <c r="X8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
         <v>89</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>90</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>91</v>
-      </c>
-      <c r="E9" t="s">
-        <v>92</v>
       </c>
       <c r="F9" t="s">
         <v>29</v>
       </c>
       <c r="G9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" t="s">
         <v>93</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="I9" t="s">
-        <v>67</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="K9">
         <v>30</v>
@@ -2091,7 +2097,7 @@
       <c r="M9" t="s">
         <v>35</v>
       </c>
-      <c r="O9" s="4">
+      <c r="O9" s="10">
         <v>0.6</v>
       </c>
       <c r="P9" t="s">
@@ -2101,40 +2107,32 @@
         <v>18</v>
       </c>
       <c r="R9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S9" t="s">
         <v>39</v>
       </c>
-      <c r="T9" t="s">
-        <v>68</v>
-      </c>
-      <c r="U9" t="s">
-        <v>40</v>
-      </c>
-      <c r="V9" t="s">
-        <v>38</v>
-      </c>
-      <c r="W9" t="s">
-        <v>68</v>
-      </c>
+      <c r="T9"/>
+      <c r="U9"/>
+      <c r="V9"/>
+      <c r="W9"/>
       <c r="X9" t="s">
         <v>41</v>
       </c>
       <c r="Y9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="3"/>
+      <c r="A10" s="11"/>
       <c r="B10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" t="s">
         <v>96</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>97</v>
-      </c>
-      <c r="D10" t="s">
-        <v>98</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -2143,16 +2141,16 @@
         <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" t="s">
         <v>66</v>
       </c>
-      <c r="I10" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>99</v>
+      <c r="J10" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="K10">
         <v>35</v>
@@ -2161,9 +2159,9 @@
         <v>40</v>
       </c>
       <c r="M10" t="s">
-        <v>100</v>
-      </c>
-      <c r="O10" s="4">
+        <v>99</v>
+      </c>
+      <c r="O10" s="10">
         <v>0.3</v>
       </c>
       <c r="P10" t="s">
@@ -2173,25 +2171,17 @@
         <v>8</v>
       </c>
       <c r="R10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S10" t="s">
         <v>38</v>
       </c>
-      <c r="T10" t="s">
-        <v>38</v>
-      </c>
-      <c r="U10" t="s">
-        <v>68</v>
-      </c>
-      <c r="V10" t="s">
-        <v>38</v>
-      </c>
-      <c r="W10" t="s">
-        <v>38</v>
-      </c>
+      <c r="T10"/>
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
       <c r="X10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y10" t="s">
         <v>42</v>
@@ -2199,13 +2189,13 @@
     </row>
     <row r="11" spans="1:25">
       <c r="B11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" t="s">
         <v>102</v>
-      </c>
-      <c r="D11" t="s">
-        <v>103</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -2213,67 +2203,58 @@
       <c r="F11" t="s">
         <v>29</v>
       </c>
-      <c r="G11" t="s">
-        <v>75</v>
-      </c>
       <c r="H11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" t="s">
         <v>66</v>
       </c>
-      <c r="I11" t="s">
-        <v>67</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>99</v>
+      <c r="J11" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="K11">
         <v>68</v>
       </c>
       <c r="L11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M11" t="s">
-        <v>100</v>
-      </c>
-      <c r="O11" s="4">
+        <v>99</v>
+      </c>
+      <c r="O11" s="10">
         <v>0.3</v>
       </c>
       <c r="P11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q11">
         <v>8</v>
       </c>
       <c r="R11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S11" t="s">
         <v>38</v>
       </c>
-      <c r="T11" t="s">
-        <v>38</v>
-      </c>
-      <c r="U11" t="s">
-        <v>68</v>
-      </c>
-      <c r="V11" t="s">
-        <v>38</v>
-      </c>
+      <c r="T11"/>
+      <c r="U11"/>
+      <c r="V11"/>
       <c r="X11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:25">
       <c r="B12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" t="s">
         <v>104</v>
-      </c>
-      <c r="D12" t="s">
-        <v>105</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -2281,28 +2262,25 @@
       <c r="F12" t="s">
         <v>29</v>
       </c>
-      <c r="G12" t="s">
-        <v>75</v>
-      </c>
       <c r="H12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" t="s">
         <v>66</v>
       </c>
-      <c r="I12" t="s">
-        <v>67</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>99</v>
+      <c r="J12" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="K12">
         <v>65</v>
       </c>
       <c r="L12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M12" t="s">
-        <v>100</v>
-      </c>
-      <c r="O12" s="4">
+        <v>99</v>
+      </c>
+      <c r="O12" s="10">
         <v>0.3</v>
       </c>
       <c r="P12" t="s">
@@ -2312,25 +2290,17 @@
         <v>8</v>
       </c>
       <c r="R12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S12" t="s">
         <v>38</v>
       </c>
-      <c r="T12" t="s">
-        <v>38</v>
-      </c>
-      <c r="U12" t="s">
-        <v>68</v>
-      </c>
-      <c r="V12" t="s">
-        <v>38</v>
-      </c>
-      <c r="W12" t="s">
-        <v>38</v>
-      </c>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
       <c r="X12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y12" t="s">
         <v>42</v>
@@ -2338,13 +2308,13 @@
     </row>
     <row r="13" spans="1:25">
       <c r="B13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -2352,17 +2322,14 @@
       <c r="F13" t="s">
         <v>29</v>
       </c>
-      <c r="G13" t="s">
-        <v>75</v>
-      </c>
       <c r="H13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I13" t="s">
-        <v>85</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>99</v>
+        <v>84</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="K13">
         <v>37</v>
@@ -2371,69 +2338,58 @@
         <v>40</v>
       </c>
       <c r="M13" t="s">
-        <v>100</v>
-      </c>
-      <c r="O13" s="4">
+        <v>99</v>
+      </c>
+      <c r="O13" s="10">
         <v>0.3</v>
       </c>
       <c r="P13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q13">
         <v>8</v>
       </c>
       <c r="R13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S13" t="s">
         <v>38</v>
       </c>
-      <c r="T13" t="s">
-        <v>38</v>
-      </c>
-      <c r="U13" t="s">
-        <v>68</v>
-      </c>
-      <c r="V13" t="s">
-        <v>38</v>
-      </c>
-      <c r="W13" t="s">
-        <v>38</v>
-      </c>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
       <c r="X13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:25">
       <c r="B14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" t="s">
         <v>108</v>
-      </c>
-      <c r="C14" t="s">
-        <v>109</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F14" t="s">
         <v>29</v>
       </c>
-      <c r="G14" t="s">
-        <v>75</v>
-      </c>
       <c r="H14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>95</v>
+        <v>84</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="K14">
         <v>80</v>
@@ -2444,7 +2400,7 @@
       <c r="M14" t="s">
         <v>35</v>
       </c>
-      <c r="O14" s="4">
+      <c r="O14" s="10">
         <v>0.8</v>
       </c>
       <c r="P14" t="s">
@@ -2454,68 +2410,57 @@
         <v>14</v>
       </c>
       <c r="R14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="S14" t="s">
         <v>39</v>
       </c>
-      <c r="T14" t="s">
-        <v>39</v>
-      </c>
-      <c r="U14" t="s">
-        <v>112</v>
-      </c>
-      <c r="V14" t="s">
-        <v>68</v>
-      </c>
-      <c r="W14" t="s">
-        <v>68</v>
-      </c>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
       <c r="X14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:25">
       <c r="B15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F15" t="s">
         <v>29</v>
       </c>
-      <c r="G15" t="s">
-        <v>75</v>
-      </c>
       <c r="H15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I15" t="s">
-        <v>67</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>95</v>
+        <v>66</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="K15">
         <v>80</v>
       </c>
       <c r="L15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M15" t="s">
         <v>35</v>
       </c>
-      <c r="O15" s="4">
+      <c r="O15" s="10">
         <v>0.6</v>
       </c>
       <c r="P15" t="s">
@@ -2525,68 +2470,60 @@
         <v>19</v>
       </c>
       <c r="R15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S15" t="s">
         <v>39</v>
       </c>
-      <c r="T15" t="s">
-        <v>68</v>
-      </c>
-      <c r="U15" t="s">
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15" t="s">
         <v>87</v>
       </c>
-      <c r="V15" t="s">
-        <v>68</v>
-      </c>
-      <c r="W15" t="s">
-        <v>38</v>
-      </c>
-      <c r="X15" t="s">
-        <v>88</v>
-      </c>
       <c r="Y15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:25">
       <c r="B16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" t="s">
         <v>116</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>117</v>
       </c>
-      <c r="D16" t="s">
-        <v>118</v>
-      </c>
       <c r="E16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F16" t="s">
         <v>29</v>
       </c>
       <c r="G16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I16" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>99</v>
+      <c r="J16" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="K16">
         <v>80</v>
       </c>
       <c r="L16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M16" t="s">
-        <v>119</v>
-      </c>
-      <c r="O16" s="4">
+        <v>118</v>
+      </c>
+      <c r="O16" s="10">
         <v>0.4</v>
       </c>
       <c r="P16" t="s">
@@ -2596,39 +2533,31 @@
         <v>16</v>
       </c>
       <c r="R16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S16" t="s">
         <v>38</v>
       </c>
-      <c r="T16" t="s">
-        <v>39</v>
-      </c>
-      <c r="U16" t="s">
-        <v>40</v>
-      </c>
-      <c r="V16" t="s">
-        <v>68</v>
-      </c>
-      <c r="W16" t="s">
-        <v>38</v>
-      </c>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
       <c r="X16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:25">
       <c r="B17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -2640,24 +2569,24 @@
         <v>30</v>
       </c>
       <c r="H17" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="I17" t="s">
-        <v>85</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>95</v>
+        <v>84</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="K17">
         <v>150</v>
       </c>
       <c r="L17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>100</v>
-      </c>
-      <c r="O17" s="4">
+        <v>99</v>
+      </c>
+      <c r="O17" s="10">
         <v>0.7</v>
       </c>
       <c r="P17" t="s">
@@ -2667,68 +2596,60 @@
         <v>2</v>
       </c>
       <c r="R17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S17" t="s">
-        <v>68</v>
-      </c>
-      <c r="T17" t="s">
-        <v>39</v>
-      </c>
-      <c r="U17" t="s">
-        <v>87</v>
-      </c>
-      <c r="V17" t="s">
-        <v>38</v>
-      </c>
-      <c r="W17" t="s">
-        <v>68</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="T17"/>
+      <c r="U17"/>
+      <c r="V17"/>
+      <c r="W17"/>
       <c r="X17" t="s">
         <v>41</v>
       </c>
       <c r="Y17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:25">
       <c r="B18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
         <v>123</v>
       </c>
       <c r="D18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F18" t="s">
         <v>29</v>
       </c>
       <c r="G18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I18" t="s">
-        <v>85</v>
-      </c>
-      <c r="J18" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J18" s="10" t="s">
         <v>33</v>
       </c>
       <c r="K18">
         <v>80</v>
       </c>
       <c r="L18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M18" t="s">
         <v>35</v>
       </c>
-      <c r="O18" s="4">
+      <c r="O18" s="10">
         <v>0.8</v>
       </c>
       <c r="P18" t="s">
@@ -2738,40 +2659,32 @@
         <v>17</v>
       </c>
       <c r="R18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S18" t="s">
-        <v>68</v>
-      </c>
-      <c r="T18" t="s">
-        <v>68</v>
-      </c>
-      <c r="U18" t="s">
-        <v>50</v>
-      </c>
-      <c r="V18" t="s">
-        <v>39</v>
-      </c>
-      <c r="W18" t="s">
-        <v>39</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
+      <c r="W18"/>
       <c r="X18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y18" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="3"/>
+      <c r="A19" s="11"/>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
         <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
         <v>125</v>
@@ -2783,13 +2696,13 @@
         <v>30</v>
       </c>
       <c r="H19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I19" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="4" t="s">
-        <v>77</v>
+      <c r="J19" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="K19">
         <v>26</v>
@@ -2798,9 +2711,9 @@
         <v>47</v>
       </c>
       <c r="M19" t="s">
-        <v>69</v>
-      </c>
-      <c r="O19" s="4">
+        <v>68</v>
+      </c>
+      <c r="O19" s="10">
         <v>0.8</v>
       </c>
       <c r="P19" t="s">
@@ -2810,33 +2723,25 @@
         <v>3</v>
       </c>
       <c r="R19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S19" t="s">
         <v>38</v>
       </c>
-      <c r="T19" t="s">
-        <v>39</v>
-      </c>
-      <c r="U19" t="s">
-        <v>60</v>
-      </c>
-      <c r="V19" t="s">
-        <v>38</v>
-      </c>
-      <c r="W19" t="s">
-        <v>38</v>
-      </c>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
+      <c r="W19"/>
       <c r="X19" t="s">
         <v>41</v>
       </c>
       <c r="Y19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:25">
       <c r="B20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
         <v>126</v>
@@ -2850,28 +2755,25 @@
       <c r="F20" t="s">
         <v>29</v>
       </c>
-      <c r="G20" t="s">
-        <v>30</v>
-      </c>
       <c r="H20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J20" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="I20" t="s">
-        <v>67</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="K20">
         <v>20</v>
       </c>
       <c r="L20" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M20" t="s">
-        <v>69</v>
-      </c>
-      <c r="O20" s="4">
+        <v>68</v>
+      </c>
+      <c r="O20" s="10">
         <v>0.7</v>
       </c>
       <c r="P20" t="s">
@@ -2881,39 +2783,31 @@
         <v>3</v>
       </c>
       <c r="R20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S20" t="s">
         <v>38</v>
       </c>
-      <c r="T20" t="s">
-        <v>39</v>
-      </c>
-      <c r="U20" t="s">
-        <v>112</v>
-      </c>
-      <c r="V20" t="s">
-        <v>38</v>
-      </c>
-      <c r="W20" t="s">
-        <v>38</v>
-      </c>
+      <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20"/>
+      <c r="W20"/>
       <c r="X20" t="s">
         <v>41</v>
       </c>
       <c r="Y20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:25">
       <c r="B21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
         <v>128</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E21" t="s">
         <v>125</v>
@@ -2921,17 +2815,14 @@
       <c r="F21" t="s">
         <v>29</v>
       </c>
-      <c r="G21" t="s">
-        <v>30</v>
-      </c>
       <c r="H21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I21" t="s">
         <v>32</v>
       </c>
-      <c r="J21" s="4" t="s">
-        <v>77</v>
+      <c r="J21" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="K21">
         <v>29</v>
@@ -2940,9 +2831,9 @@
         <v>40</v>
       </c>
       <c r="M21" t="s">
-        <v>69</v>
-      </c>
-      <c r="O21" s="4">
+        <v>68</v>
+      </c>
+      <c r="O21" s="10">
         <v>0.8</v>
       </c>
       <c r="P21" t="s">
@@ -2952,33 +2843,25 @@
         <v>3</v>
       </c>
       <c r="R21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S21" t="s">
         <v>38</v>
       </c>
-      <c r="T21" t="s">
-        <v>39</v>
-      </c>
-      <c r="U21" t="s">
-        <v>40</v>
-      </c>
-      <c r="V21" t="s">
-        <v>38</v>
-      </c>
-      <c r="W21" t="s">
-        <v>38</v>
-      </c>
+      <c r="T21"/>
+      <c r="U21"/>
+      <c r="V21"/>
+      <c r="W21"/>
       <c r="X21" t="s">
         <v>41</v>
       </c>
       <c r="Y21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:25">
       <c r="B22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
         <v>129</v>
@@ -2992,28 +2875,25 @@
       <c r="F22" t="s">
         <v>29</v>
       </c>
-      <c r="G22" t="s">
-        <v>30</v>
-      </c>
       <c r="H22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I22" t="s">
         <v>32</v>
       </c>
-      <c r="J22" s="4" t="s">
-        <v>77</v>
+      <c r="J22" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="K22">
         <v>14</v>
       </c>
       <c r="L22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M22" t="s">
-        <v>69</v>
-      </c>
-      <c r="O22" s="4">
+        <v>68</v>
+      </c>
+      <c r="O22" s="10">
         <v>0.7</v>
       </c>
       <c r="P22" t="s">
@@ -3023,33 +2903,25 @@
         <v>3</v>
       </c>
       <c r="R22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S22" t="s">
         <v>38</v>
       </c>
-      <c r="T22" t="s">
-        <v>39</v>
-      </c>
-      <c r="U22" t="s">
-        <v>112</v>
-      </c>
-      <c r="V22" t="s">
-        <v>38</v>
-      </c>
-      <c r="W22" t="s">
-        <v>38</v>
-      </c>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
       <c r="X22" t="s">
         <v>41</v>
       </c>
       <c r="Y22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:25">
       <c r="B23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C23" t="s">
         <v>131</v>
@@ -3058,33 +2930,33 @@
         <v>132</v>
       </c>
       <c r="E23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F23" t="s">
         <v>29</v>
       </c>
       <c r="G23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H23" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="I23" t="s">
+        <v>84</v>
+      </c>
+      <c r="J23" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="K23">
         <v>200</v>
       </c>
       <c r="L23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M23" t="s">
-        <v>119</v>
-      </c>
-      <c r="O23" s="4">
+        <v>118</v>
+      </c>
+      <c r="O23" s="10">
         <v>0.4</v>
       </c>
       <c r="P23" t="s">
@@ -3094,23 +2966,15 @@
         <v>12</v>
       </c>
       <c r="R23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S23" t="s">
         <v>38</v>
       </c>
-      <c r="T23" t="s">
-        <v>39</v>
-      </c>
-      <c r="U23" t="s">
-        <v>50</v>
-      </c>
-      <c r="V23" t="s">
-        <v>38</v>
-      </c>
-      <c r="W23" t="s">
-        <v>38</v>
-      </c>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
+      <c r="W23"/>
       <c r="X23" t="s">
         <v>133</v>
       </c>
@@ -3120,13 +2984,13 @@
     </row>
     <row r="24" spans="1:25">
       <c r="B24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
         <v>134</v>
       </c>
       <c r="D24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E24" t="s">
         <v>125</v>
@@ -3134,28 +2998,25 @@
       <c r="F24" t="s">
         <v>29</v>
       </c>
-      <c r="G24" t="s">
-        <v>93</v>
-      </c>
       <c r="H24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I24" t="s">
         <v>32</v>
       </c>
-      <c r="J24" s="4" t="s">
-        <v>86</v>
+      <c r="J24" s="10" t="s">
+        <v>85</v>
       </c>
       <c r="K24">
         <v>80</v>
       </c>
       <c r="L24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M24" t="s">
-        <v>69</v>
-      </c>
-      <c r="O24" s="4">
+        <v>68</v>
+      </c>
+      <c r="O24" s="10">
         <v>1</v>
       </c>
       <c r="P24" t="s">
@@ -3165,42 +3026,34 @@
         <v>11</v>
       </c>
       <c r="R24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S24" t="s">
         <v>38</v>
       </c>
-      <c r="T24" t="s">
-        <v>68</v>
-      </c>
-      <c r="U24" t="s">
+      <c r="T24"/>
+      <c r="U24"/>
+      <c r="V24"/>
+      <c r="W24"/>
+      <c r="X24" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y24" t="s">
         <v>87</v>
-      </c>
-      <c r="V24" t="s">
-        <v>68</v>
-      </c>
-      <c r="W24" t="s">
-        <v>38</v>
-      </c>
-      <c r="X24" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:25">
       <c r="B25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
         <v>135</v>
       </c>
       <c r="D25" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" t="s">
         <v>91</v>
-      </c>
-      <c r="E25" t="s">
-        <v>92</v>
       </c>
       <c r="F25" t="s">
         <v>29</v>
@@ -3209,24 +3062,24 @@
         <v>30</v>
       </c>
       <c r="H25" t="s">
+        <v>75</v>
+      </c>
+      <c r="I25" t="s">
+        <v>66</v>
+      </c>
+      <c r="J25" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="I25" t="s">
-        <v>67</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M25" t="s">
-        <v>119</v>
-      </c>
-      <c r="O25" s="4">
+        <v>118</v>
+      </c>
+      <c r="O25" s="10">
         <v>0.6</v>
       </c>
       <c r="P25" t="s">
@@ -3236,33 +3089,25 @@
         <v>12</v>
       </c>
       <c r="R25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S25" t="s">
         <v>39</v>
       </c>
-      <c r="T25" t="s">
-        <v>38</v>
-      </c>
-      <c r="U25" t="s">
-        <v>40</v>
-      </c>
-      <c r="V25" t="s">
-        <v>68</v>
-      </c>
-      <c r="W25" t="s">
-        <v>38</v>
-      </c>
+      <c r="T25"/>
+      <c r="U25"/>
+      <c r="V25"/>
+      <c r="W25"/>
       <c r="X25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:25">
       <c r="B26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
         <v>136</v>
@@ -3277,16 +3122,16 @@
         <v>29</v>
       </c>
       <c r="G26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H26" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26" t="s">
+        <v>84</v>
+      </c>
+      <c r="J26" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="I26" t="s">
-        <v>85</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="K26">
         <v>80</v>
@@ -3295,46 +3140,38 @@
         <v>40</v>
       </c>
       <c r="M26" t="s">
-        <v>119</v>
-      </c>
-      <c r="O26" s="4">
+        <v>118</v>
+      </c>
+      <c r="O26" s="10">
         <v>0.7</v>
       </c>
       <c r="P26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q26">
         <v>10</v>
       </c>
       <c r="R26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S26" t="s">
-        <v>68</v>
-      </c>
-      <c r="T26" t="s">
-        <v>38</v>
-      </c>
-      <c r="U26" t="s">
-        <v>68</v>
-      </c>
-      <c r="V26" t="s">
-        <v>39</v>
-      </c>
-      <c r="W26" t="s">
-        <v>39</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="T26"/>
+      <c r="U26"/>
+      <c r="V26"/>
+      <c r="W26"/>
       <c r="X26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:25">
-      <c r="A27" s="3"/>
+      <c r="A27" s="11"/>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
         <v>139</v>
@@ -3352,24 +3189,24 @@
         <v>30</v>
       </c>
       <c r="H27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I27" t="s">
         <v>46</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="J27" s="10" t="s">
         <v>33</v>
       </c>
       <c r="K27">
         <v>48</v>
       </c>
       <c r="L27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M27" t="s">
-        <v>119</v>
-      </c>
-      <c r="O27" s="4">
+        <v>118</v>
+      </c>
+      <c r="O27" s="10">
         <v>0.7</v>
       </c>
       <c r="P27" t="s">
@@ -3379,7 +3216,7 @@
         <v>12</v>
       </c>
       <c r="R27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S27" t="s">
         <v>38</v>
@@ -3388,7 +3225,7 @@
         <v>39</v>
       </c>
       <c r="U27" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="V27" t="s">
         <v>39</v>
@@ -3397,15 +3234,15 @@
         <v>38</v>
       </c>
       <c r="X27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="B28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
         <v>141</v>
@@ -3419,28 +3256,25 @@
       <c r="F28" t="s">
         <v>29</v>
       </c>
-      <c r="G28" t="s">
-        <v>30</v>
-      </c>
       <c r="H28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I28" t="s">
         <v>46</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="J28" s="10" t="s">
         <v>33</v>
       </c>
       <c r="K28">
         <v>33</v>
       </c>
       <c r="L28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M28" t="s">
-        <v>119</v>
-      </c>
-      <c r="O28" s="4">
+        <v>118</v>
+      </c>
+      <c r="O28" s="10">
         <v>0.8</v>
       </c>
       <c r="P28" t="s">
@@ -3450,7 +3284,7 @@
         <v>12</v>
       </c>
       <c r="R28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S28" t="s">
         <v>38</v>
@@ -3468,15 +3302,15 @@
         <v>38</v>
       </c>
       <c r="X28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:25">
       <c r="B29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
         <v>143</v>
@@ -3490,16 +3324,13 @@
       <c r="F29" t="s">
         <v>29</v>
       </c>
-      <c r="G29" t="s">
-        <v>30</v>
-      </c>
       <c r="H29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I29" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="4" t="s">
+      <c r="J29" s="10" t="s">
         <v>33</v>
       </c>
       <c r="K29">
@@ -3509,9 +3340,9 @@
         <v>40</v>
       </c>
       <c r="M29" t="s">
-        <v>119</v>
-      </c>
-      <c r="O29" s="4">
+        <v>118</v>
+      </c>
+      <c r="O29" s="10">
         <v>0.6</v>
       </c>
       <c r="P29" t="s">
@@ -3521,7 +3352,7 @@
         <v>12</v>
       </c>
       <c r="R29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S29" t="s">
         <v>38</v>
@@ -3539,21 +3370,21 @@
         <v>38</v>
       </c>
       <c r="X29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:25">
       <c r="B30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
         <v>145</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E30" t="s">
         <v>140</v>
@@ -3561,16 +3392,13 @@
       <c r="F30" t="s">
         <v>29</v>
       </c>
-      <c r="G30" t="s">
-        <v>30</v>
-      </c>
       <c r="H30" t="s">
+        <v>65</v>
+      </c>
+      <c r="I30" t="s">
         <v>66</v>
       </c>
-      <c r="I30" t="s">
-        <v>67</v>
-      </c>
-      <c r="J30" s="4" t="s">
+      <c r="J30" s="10" t="s">
         <v>33</v>
       </c>
       <c r="K30">
@@ -3580,9 +3408,9 @@
         <v>34</v>
       </c>
       <c r="M30" t="s">
-        <v>119</v>
-      </c>
-      <c r="O30" s="4">
+        <v>118</v>
+      </c>
+      <c r="O30" s="10">
         <v>0.7</v>
       </c>
       <c r="P30" t="s">
@@ -3592,7 +3420,7 @@
         <v>12</v>
       </c>
       <c r="R30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S30" t="s">
         <v>38</v>
@@ -3601,7 +3429,7 @@
         <v>39</v>
       </c>
       <c r="U30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V30" t="s">
         <v>39</v>
@@ -3610,50 +3438,47 @@
         <v>38</v>
       </c>
       <c r="X30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:25">
       <c r="B31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
         <v>146</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F31" t="s">
         <v>29</v>
       </c>
-      <c r="G31" t="s">
-        <v>30</v>
-      </c>
       <c r="H31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I31" t="s">
-        <v>67</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="K31">
         <v>80</v>
       </c>
       <c r="L31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M31" t="s">
-        <v>100</v>
-      </c>
-      <c r="O31" s="4">
+        <v>99</v>
+      </c>
+      <c r="O31" s="10">
         <v>0.9</v>
       </c>
       <c r="P31" t="s">
@@ -3663,25 +3488,25 @@
         <v>14</v>
       </c>
       <c r="R31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S31" t="s">
         <v>38</v>
       </c>
       <c r="T31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U31" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="V31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="W31" t="s">
         <v>38</v>
       </c>
       <c r="X31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y31" t="s">
         <v>42</v>
@@ -3689,13 +3514,13 @@
     </row>
     <row r="32" spans="1:25">
       <c r="B32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s">
         <v>147</v>
       </c>
       <c r="D32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E32" t="s">
         <v>140</v>
@@ -3703,28 +3528,25 @@
       <c r="F32" t="s">
         <v>29</v>
       </c>
-      <c r="G32" t="s">
-        <v>30</v>
-      </c>
       <c r="H32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I32" t="s">
-        <v>85</v>
-      </c>
-      <c r="J32" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J32" s="10" t="s">
         <v>33</v>
       </c>
       <c r="K32">
         <v>200</v>
       </c>
       <c r="L32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M32" t="s">
-        <v>119</v>
-      </c>
-      <c r="O32" s="4">
+        <v>118</v>
+      </c>
+      <c r="O32" s="10">
         <v>0.5</v>
       </c>
       <c r="P32" t="s">
@@ -3734,7 +3556,7 @@
         <v>4</v>
       </c>
       <c r="R32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S32" t="s">
         <v>39</v>
@@ -3743,24 +3565,24 @@
         <v>39</v>
       </c>
       <c r="U32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="W32" t="s">
         <v>39</v>
       </c>
       <c r="X32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:25">
       <c r="B33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
         <v>148</v>
@@ -3769,22 +3591,22 @@
         <v>149</v>
       </c>
       <c r="E33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F33" t="s">
         <v>29</v>
       </c>
       <c r="G33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I33" t="s">
         <v>32</v>
       </c>
-      <c r="J33" s="4" t="s">
-        <v>95</v>
+      <c r="J33" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="K33">
         <v>150</v>
@@ -3793,9 +3615,9 @@
         <v>47</v>
       </c>
       <c r="M33" t="s">
-        <v>69</v>
-      </c>
-      <c r="O33" s="4">
+        <v>68</v>
+      </c>
+      <c r="O33" s="10">
         <v>0.8</v>
       </c>
       <c r="P33" t="s">
@@ -3805,7 +3627,7 @@
         <v>5</v>
       </c>
       <c r="R33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S33" t="s">
         <v>38</v>
@@ -3814,7 +3636,7 @@
         <v>39</v>
       </c>
       <c r="U33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V33" t="s">
         <v>39</v>
@@ -3823,21 +3645,21 @@
         <v>39</v>
       </c>
       <c r="X33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:25">
       <c r="B34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
         <v>150</v>
       </c>
       <c r="D34" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E34" t="s">
         <v>138</v>
@@ -3845,28 +3667,25 @@
       <c r="F34" t="s">
         <v>29</v>
       </c>
-      <c r="G34" t="s">
-        <v>65</v>
-      </c>
       <c r="H34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I34" t="s">
         <v>46</v>
       </c>
-      <c r="J34" s="4" t="s">
-        <v>77</v>
+      <c r="J34" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="K34">
         <v>100</v>
       </c>
       <c r="L34" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M34" t="s">
-        <v>100</v>
-      </c>
-      <c r="O34" s="4">
+        <v>99</v>
+      </c>
+      <c r="O34" s="10">
         <v>0.6</v>
       </c>
       <c r="P34" t="s">
@@ -3879,7 +3698,7 @@
         <v>37</v>
       </c>
       <c r="S34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T34" t="s">
         <v>38</v>
@@ -3894,16 +3713,16 @@
         <v>38</v>
       </c>
       <c r="X34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="3"/>
+      <c r="A35" s="11"/>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C35" t="s">
         <v>151</v>
@@ -3912,7 +3731,7 @@
         <v>152</v>
       </c>
       <c r="E35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F35" t="s">
         <v>29</v>
@@ -3921,13 +3740,13 @@
         <v>30</v>
       </c>
       <c r="H35" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="I35" t="s">
         <v>32</v>
       </c>
-      <c r="J35" s="4" t="s">
-        <v>95</v>
+      <c r="J35" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="K35">
         <v>131</v>
@@ -3936,19 +3755,19 @@
         <v>40</v>
       </c>
       <c r="M35" t="s">
-        <v>119</v>
-      </c>
-      <c r="O35" s="4">
+        <v>118</v>
+      </c>
+      <c r="O35" s="10">
         <v>0.4</v>
       </c>
       <c r="P35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q35">
         <v>14</v>
       </c>
       <c r="R35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S35" t="s">
         <v>38</v>
@@ -3957,7 +3776,7 @@
         <v>38</v>
       </c>
       <c r="U35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V35" t="s">
         <v>38</v>
@@ -3969,12 +3788,12 @@
         <v>41</v>
       </c>
       <c r="Y35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:25">
       <c r="B36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C36" t="s">
         <v>153</v>
@@ -3983,22 +3802,19 @@
         <v>154</v>
       </c>
       <c r="E36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F36" t="s">
         <v>29</v>
       </c>
-      <c r="G36" t="s">
-        <v>30</v>
-      </c>
       <c r="H36" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="I36" t="s">
         <v>32</v>
       </c>
-      <c r="J36" s="4" t="s">
-        <v>95</v>
+      <c r="J36" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="K36">
         <v>126</v>
@@ -4007,19 +3823,19 @@
         <v>47</v>
       </c>
       <c r="M36" t="s">
-        <v>119</v>
-      </c>
-      <c r="O36" s="4">
+        <v>118</v>
+      </c>
+      <c r="O36" s="10">
         <v>0.6</v>
       </c>
       <c r="P36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q36">
         <v>14</v>
       </c>
       <c r="R36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S36" t="s">
         <v>38</v>
@@ -4028,7 +3844,7 @@
         <v>38</v>
       </c>
       <c r="U36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V36" t="s">
         <v>38</v>
@@ -4040,12 +3856,12 @@
         <v>41</v>
       </c>
       <c r="Y36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:25">
       <c r="B37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C37" t="s">
         <v>155</v>
@@ -4059,28 +3875,25 @@
       <c r="F37" t="s">
         <v>29</v>
       </c>
-      <c r="G37" t="s">
-        <v>30</v>
-      </c>
       <c r="H37" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I37" t="s">
-        <v>85</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>77</v>
+        <v>84</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="K37">
         <v>30</v>
       </c>
       <c r="L37" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M37" t="s">
         <v>35</v>
       </c>
-      <c r="O37" s="4">
+      <c r="O37" s="10">
         <v>0.5</v>
       </c>
       <c r="P37" t="s">
@@ -4090,7 +3903,7 @@
         <v>6</v>
       </c>
       <c r="R37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S37" t="s">
         <v>38</v>
@@ -4099,28 +3912,36 @@
         <v>38</v>
       </c>
       <c r="U37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="W37" t="s">
         <v>38</v>
       </c>
       <c r="X37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="13">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A19:A22"/>
     <mergeCell ref="A27:A30"/>
     <mergeCell ref="A35:A36"/>
+    <mergeCell ref="G2:G5"/>
+    <mergeCell ref="G10:G15"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="G27:G32"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="H2:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/test_read_copy.xlsx
+++ b/test_read_copy.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="11855"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
-    <sheet name="0330需求列表" sheetId="1" r:id="rId1"/>
+    <sheet name="0330测试计划" sheetId="2" r:id="rId1"/>
+    <sheet name="0330需求列表" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="157">
+  <si>
+    <t>发生发的</t>
+  </si>
   <si>
     <t>特性分类</t>
   </si>
@@ -1535,6 +1539,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Y37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
@@ -1544,2387 +1565,2304 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:25">
       <c r="A2" s="4"/>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K2" s="1">
         <v>50</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O2" s="6">
         <v>0.8</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="1">
         <v>6</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="V2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="X2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:25">
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K3" s="1">
         <v>30</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O3" s="6">
         <v>0.7</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q3" s="1">
         <v>6</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:25">
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K4" s="1">
         <v>35</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O4" s="6">
         <v>0.8</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q4" s="1">
         <v>6</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:25">
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K5" s="1">
         <v>26</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O5" s="6">
         <v>0.8</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q5" s="1">
         <v>6</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:25">
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K6">
         <v>150</v>
       </c>
       <c r="L6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O6" s="10">
         <v>0.6</v>
       </c>
       <c r="P6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q6">
         <v>3</v>
       </c>
       <c r="R6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T6"/>
-      <c r="U6"/>
-      <c r="V6"/>
-      <c r="W6"/>
+        <v>40</v>
+      </c>
       <c r="X6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:25">
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7">
         <v>30</v>
       </c>
       <c r="L7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O7" s="10">
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q7">
         <v>5</v>
       </c>
       <c r="R7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S7" t="s">
-        <v>38</v>
-      </c>
-      <c r="T7"/>
-      <c r="U7"/>
-      <c r="V7"/>
-      <c r="W7"/>
+        <v>39</v>
+      </c>
       <c r="X7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:25">
       <c r="B8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K8">
         <v>150</v>
       </c>
       <c r="L8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O8" s="10">
         <v>0.4</v>
       </c>
       <c r="P8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S8" t="s">
-        <v>67</v>
-      </c>
-      <c r="T8"/>
-      <c r="U8"/>
-      <c r="V8"/>
-      <c r="W8"/>
+        <v>68</v>
+      </c>
       <c r="X8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K9">
         <v>30</v>
       </c>
       <c r="L9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O9" s="10">
         <v>0.6</v>
       </c>
       <c r="P9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q9">
         <v>18</v>
       </c>
       <c r="R9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S9" t="s">
-        <v>39</v>
-      </c>
-      <c r="T9"/>
-      <c r="U9"/>
-      <c r="V9"/>
-      <c r="W9"/>
+        <v>40</v>
+      </c>
       <c r="X9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="11"/>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K10">
         <v>35</v>
       </c>
       <c r="L10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O10" s="10">
         <v>0.3</v>
       </c>
       <c r="P10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q10">
         <v>8</v>
       </c>
       <c r="R10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S10" t="s">
-        <v>38</v>
-      </c>
-      <c r="T10"/>
-      <c r="U10"/>
-      <c r="V10"/>
-      <c r="W10"/>
+        <v>39</v>
+      </c>
       <c r="X10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:25">
       <c r="B11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K11">
         <v>68</v>
       </c>
       <c r="L11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O11" s="10">
         <v>0.3</v>
       </c>
       <c r="P11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q11">
         <v>8</v>
       </c>
       <c r="R11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S11" t="s">
-        <v>38</v>
-      </c>
-      <c r="T11"/>
-      <c r="U11"/>
-      <c r="V11"/>
+        <v>39</v>
+      </c>
       <c r="X11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:25">
       <c r="B12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K12">
         <v>65</v>
       </c>
       <c r="L12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O12" s="10">
         <v>0.3</v>
       </c>
       <c r="P12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q12">
         <v>8</v>
       </c>
       <c r="R12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S12" t="s">
-        <v>38</v>
-      </c>
-      <c r="T12"/>
-      <c r="U12"/>
-      <c r="V12"/>
-      <c r="W12"/>
+        <v>39</v>
+      </c>
       <c r="X12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:25">
       <c r="B13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K13">
         <v>37</v>
       </c>
       <c r="L13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O13" s="10">
         <v>0.3</v>
       </c>
       <c r="P13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q13">
         <v>8</v>
       </c>
       <c r="R13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S13" t="s">
-        <v>38</v>
-      </c>
-      <c r="T13"/>
-      <c r="U13"/>
-      <c r="V13"/>
-      <c r="W13"/>
+        <v>39</v>
+      </c>
       <c r="X13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:25">
       <c r="B14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K14">
         <v>80</v>
       </c>
       <c r="L14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O14" s="10">
         <v>0.8</v>
       </c>
       <c r="P14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q14">
         <v>14</v>
       </c>
       <c r="R14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S14" t="s">
-        <v>39</v>
-      </c>
-      <c r="T14"/>
-      <c r="U14"/>
-      <c r="V14"/>
-      <c r="W14"/>
+        <v>40</v>
+      </c>
       <c r="X14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:25">
       <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" t="s">
+        <v>67</v>
+      </c>
+      <c r="J15" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="C15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D15" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" t="s">
-        <v>109</v>
-      </c>
-      <c r="F15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" t="s">
-        <v>113</v>
-      </c>
-      <c r="I15" t="s">
-        <v>66</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>94</v>
       </c>
       <c r="K15">
         <v>80</v>
       </c>
       <c r="L15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O15" s="10">
         <v>0.6</v>
       </c>
       <c r="P15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q15">
         <v>19</v>
       </c>
       <c r="R15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T15"/>
-      <c r="U15"/>
-      <c r="V15"/>
-      <c r="W15"/>
+        <v>40</v>
+      </c>
       <c r="X15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:25">
       <c r="B16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K16">
         <v>80</v>
       </c>
       <c r="L16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O16" s="10">
         <v>0.4</v>
       </c>
       <c r="P16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q16">
         <v>16</v>
       </c>
       <c r="R16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S16" t="s">
-        <v>38</v>
-      </c>
-      <c r="T16"/>
-      <c r="U16"/>
-      <c r="V16"/>
-      <c r="W16"/>
+        <v>39</v>
+      </c>
       <c r="X16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:25">
       <c r="B17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K17">
         <v>150</v>
       </c>
       <c r="L17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O17" s="10">
         <v>0.7</v>
       </c>
       <c r="P17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q17">
         <v>2</v>
       </c>
       <c r="R17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S17" t="s">
-        <v>67</v>
-      </c>
-      <c r="T17"/>
-      <c r="U17"/>
-      <c r="V17"/>
-      <c r="W17"/>
+        <v>68</v>
+      </c>
       <c r="X17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:25">
       <c r="B18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K18">
         <v>80</v>
       </c>
       <c r="L18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O18" s="10">
         <v>0.8</v>
       </c>
       <c r="P18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q18">
         <v>17</v>
       </c>
       <c r="R18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S18" t="s">
-        <v>67</v>
-      </c>
-      <c r="T18"/>
-      <c r="U18"/>
-      <c r="V18"/>
-      <c r="W18"/>
+        <v>68</v>
+      </c>
       <c r="X18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="11"/>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K19">
         <v>26</v>
       </c>
       <c r="L19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O19" s="10">
         <v>0.8</v>
       </c>
       <c r="P19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q19">
         <v>3</v>
       </c>
       <c r="R19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S19" t="s">
-        <v>38</v>
-      </c>
-      <c r="T19"/>
-      <c r="U19"/>
-      <c r="V19"/>
-      <c r="W19"/>
+        <v>39</v>
+      </c>
       <c r="X19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:25">
       <c r="B20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" t="s">
         <v>126</v>
       </c>
-      <c r="D20" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" t="s">
-        <v>125</v>
-      </c>
       <c r="F20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K20">
         <v>20</v>
       </c>
       <c r="L20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O20" s="10">
         <v>0.7</v>
       </c>
       <c r="P20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q20">
         <v>3</v>
       </c>
       <c r="R20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S20" t="s">
-        <v>38</v>
-      </c>
-      <c r="T20"/>
-      <c r="U20"/>
-      <c r="V20"/>
-      <c r="W20"/>
+        <v>39</v>
+      </c>
       <c r="X20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:25">
       <c r="B21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K21">
         <v>29</v>
       </c>
       <c r="L21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O21" s="10">
         <v>0.8</v>
       </c>
       <c r="P21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q21">
         <v>3</v>
       </c>
       <c r="R21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S21" t="s">
-        <v>38</v>
-      </c>
-      <c r="T21"/>
-      <c r="U21"/>
-      <c r="V21"/>
-      <c r="W21"/>
+        <v>39</v>
+      </c>
       <c r="X21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" ht="16" customHeight="1" spans="1:25">
       <c r="B22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K22">
         <v>14</v>
       </c>
       <c r="L22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O22" s="10">
         <v>0.7</v>
       </c>
       <c r="P22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q22">
         <v>3</v>
       </c>
       <c r="R22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S22" t="s">
-        <v>38</v>
-      </c>
-      <c r="T22"/>
-      <c r="U22"/>
-      <c r="V22"/>
-      <c r="W22"/>
+        <v>39</v>
+      </c>
       <c r="X22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:25">
       <c r="B23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K23">
         <v>200</v>
       </c>
       <c r="L23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O23" s="10">
         <v>0.4</v>
       </c>
       <c r="P23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q23">
         <v>12</v>
       </c>
       <c r="R23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S23" t="s">
-        <v>38</v>
-      </c>
-      <c r="T23"/>
-      <c r="U23"/>
-      <c r="V23"/>
-      <c r="W23"/>
+        <v>39</v>
+      </c>
       <c r="X23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Y23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:25">
       <c r="B24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K24">
         <v>80</v>
       </c>
       <c r="L24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O24" s="10">
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q24">
         <v>11</v>
       </c>
       <c r="R24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S24" t="s">
-        <v>38</v>
-      </c>
-      <c r="T24"/>
-      <c r="U24"/>
-      <c r="V24"/>
-      <c r="W24"/>
+        <v>39</v>
+      </c>
       <c r="X24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:25">
       <c r="B25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O25" s="10">
         <v>0.6</v>
       </c>
       <c r="P25" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q25">
         <v>12</v>
       </c>
       <c r="R25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S25" t="s">
-        <v>39</v>
-      </c>
-      <c r="T25"/>
-      <c r="U25"/>
-      <c r="V25"/>
-      <c r="W25"/>
+        <v>40</v>
+      </c>
       <c r="X25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:25">
       <c r="B26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K26">
         <v>80</v>
       </c>
       <c r="L26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O26" s="10">
         <v>0.7</v>
       </c>
       <c r="P26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q26">
         <v>10</v>
       </c>
       <c r="R26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S26" t="s">
-        <v>67</v>
-      </c>
-      <c r="T26"/>
-      <c r="U26"/>
-      <c r="V26"/>
-      <c r="W26"/>
+        <v>68</v>
+      </c>
       <c r="X26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="11"/>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K27">
         <v>48</v>
       </c>
       <c r="L27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O27" s="10">
         <v>0.7</v>
       </c>
       <c r="P27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q27">
         <v>12</v>
       </c>
       <c r="R27" t="s">
+        <v>56</v>
+      </c>
+      <c r="S27" t="s">
+        <v>39</v>
+      </c>
+      <c r="T27" t="s">
+        <v>40</v>
+      </c>
+      <c r="U27" t="s">
         <v>55</v>
       </c>
-      <c r="S27" t="s">
-        <v>38</v>
-      </c>
-      <c r="T27" t="s">
+      <c r="V27" t="s">
+        <v>40</v>
+      </c>
+      <c r="W27" t="s">
         <v>39</v>
       </c>
-      <c r="U27" t="s">
-        <v>54</v>
-      </c>
-      <c r="V27" t="s">
-        <v>39</v>
-      </c>
-      <c r="W27" t="s">
-        <v>38</v>
-      </c>
       <c r="X27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="B28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" t="s">
+        <v>143</v>
+      </c>
+      <c r="E28" t="s">
         <v>141</v>
       </c>
-      <c r="D28" t="s">
-        <v>142</v>
-      </c>
-      <c r="E28" t="s">
-        <v>140</v>
-      </c>
       <c r="F28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K28">
         <v>33</v>
       </c>
       <c r="L28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O28" s="10">
         <v>0.8</v>
       </c>
       <c r="P28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q28">
         <v>12</v>
       </c>
       <c r="R28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T28" t="s">
+        <v>40</v>
+      </c>
+      <c r="U28" t="s">
+        <v>41</v>
+      </c>
+      <c r="V28" t="s">
+        <v>40</v>
+      </c>
+      <c r="W28" t="s">
         <v>39</v>
       </c>
-      <c r="U28" t="s">
-        <v>40</v>
-      </c>
-      <c r="V28" t="s">
-        <v>39</v>
-      </c>
-      <c r="W28" t="s">
-        <v>38</v>
-      </c>
       <c r="X28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:25">
       <c r="B29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K29">
         <v>11</v>
       </c>
       <c r="L29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O29" s="10">
         <v>0.6</v>
       </c>
       <c r="P29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q29">
         <v>12</v>
       </c>
       <c r="R29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T29" t="s">
+        <v>40</v>
+      </c>
+      <c r="U29" t="s">
+        <v>41</v>
+      </c>
+      <c r="V29" t="s">
+        <v>40</v>
+      </c>
+      <c r="W29" t="s">
         <v>39</v>
       </c>
-      <c r="U29" t="s">
-        <v>40</v>
-      </c>
-      <c r="V29" t="s">
-        <v>39</v>
-      </c>
-      <c r="W29" t="s">
-        <v>38</v>
-      </c>
       <c r="X29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:25">
       <c r="B30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K30">
         <v>24</v>
       </c>
       <c r="L30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O30" s="10">
         <v>0.7</v>
       </c>
       <c r="P30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q30">
         <v>12</v>
       </c>
       <c r="R30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T30" t="s">
+        <v>40</v>
+      </c>
+      <c r="U30" t="s">
+        <v>60</v>
+      </c>
+      <c r="V30" t="s">
+        <v>40</v>
+      </c>
+      <c r="W30" t="s">
         <v>39</v>
       </c>
-      <c r="U30" t="s">
-        <v>59</v>
-      </c>
-      <c r="V30" t="s">
-        <v>39</v>
-      </c>
-      <c r="W30" t="s">
-        <v>38</v>
-      </c>
       <c r="X30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:25">
       <c r="B31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K31">
         <v>80</v>
       </c>
       <c r="L31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O31" s="10">
         <v>0.9</v>
       </c>
       <c r="P31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q31">
         <v>14</v>
       </c>
       <c r="R31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="U31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="W31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:25">
       <c r="B32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K32">
         <v>200</v>
       </c>
       <c r="L32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="10">
         <v>0.5</v>
       </c>
       <c r="P32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q32">
         <v>4</v>
       </c>
       <c r="R32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="V32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="W32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:25">
       <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D33" t="s">
+        <v>150</v>
+      </c>
+      <c r="E33" t="s">
+        <v>64</v>
+      </c>
+      <c r="F33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" t="s">
+        <v>65</v>
+      </c>
+      <c r="H33" t="s">
+        <v>84</v>
+      </c>
+      <c r="I33" t="s">
+        <v>33</v>
+      </c>
+      <c r="J33" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="C33" t="s">
-        <v>148</v>
-      </c>
-      <c r="D33" t="s">
-        <v>149</v>
-      </c>
-      <c r="E33" t="s">
-        <v>63</v>
-      </c>
-      <c r="F33" t="s">
-        <v>29</v>
-      </c>
-      <c r="G33" t="s">
-        <v>64</v>
-      </c>
-      <c r="H33" t="s">
-        <v>83</v>
-      </c>
-      <c r="I33" t="s">
-        <v>32</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>94</v>
       </c>
       <c r="K33">
         <v>150</v>
       </c>
       <c r="L33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O33" s="10">
         <v>0.8</v>
       </c>
       <c r="P33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q33">
         <v>5</v>
       </c>
       <c r="R33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:25">
       <c r="B34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K34">
         <v>100</v>
       </c>
       <c r="L34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O34" s="10">
         <v>0.6</v>
       </c>
       <c r="P34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q34">
         <v>20</v>
       </c>
       <c r="R34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V34" t="s">
+        <v>40</v>
+      </c>
+      <c r="W34" t="s">
         <v>39</v>
       </c>
-      <c r="W34" t="s">
-        <v>38</v>
-      </c>
       <c r="X34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="11"/>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D35" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K35">
         <v>131</v>
       </c>
       <c r="L35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O35" s="10">
         <v>0.4</v>
       </c>
       <c r="P35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q35">
         <v>14</v>
       </c>
       <c r="R35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:25">
       <c r="B36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D36" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K36">
         <v>126</v>
       </c>
       <c r="L36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M36" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O36" s="10">
         <v>0.6</v>
       </c>
       <c r="P36" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q36">
         <v>14</v>
       </c>
       <c r="R36" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U36" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y36" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:25">
       <c r="B37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H37" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K37">
         <v>30</v>
       </c>
       <c r="L37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O37" s="10">
         <v>0.5</v>
       </c>
       <c r="P37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q37">
         <v>6</v>
       </c>
       <c r="R37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V37" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="W37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
